--- a/customers/amir hosein.xlsx
+++ b/customers/amir hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>وجه آرایشگاه</t>
   </si>
 </sst>
 </file>
@@ -586,7 +592,7 @@
       </c>
       <c r="H2" s="7">
         <f>C27</f>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -810,17 +816,23 @@
     <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <f t="shared" ref="A17:A24" si="1">A16+B17-C17</f>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="C17" s="6">
+        <v>7200000</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -830,7 +842,7 @@
     <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -840,7 +852,7 @@
     <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -850,7 +862,7 @@
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -860,7 +872,7 @@
     <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -870,7 +882,7 @@
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -880,7 +892,7 @@
     <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <f t="shared" si="1"/>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -894,7 +906,7 @@
       </c>
       <c r="C25" s="7">
         <f>SUM(C3:C24)</f>
-        <v>35000</v>
+        <v>7235000</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -904,7 +916,7 @@
       </c>
       <c r="C27" s="10">
         <f>A24</f>
-        <v>4981000</v>
+        <v>-2219000</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>

--- a/customers/amir hosein.xlsx
+++ b/customers/amir hosein.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -130,6 +130,12 @@
   </si>
   <si>
     <t>وجه آرایشگاه</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>وجه گرفته (کارت به کارت)</t>
   </si>
 </sst>
 </file>
@@ -560,7 +566,7 @@
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="16.875" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
@@ -592,7 +598,7 @@
       </c>
       <c r="H2" s="7">
         <f>C27</f>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -832,17 +838,23 @@
     <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="B18" s="6">
+        <v>2219000</v>
+      </c>
       <c r="C18" s="6"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="D18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -852,7 +864,7 @@
     <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -862,7 +874,7 @@
     <row r="21" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -872,7 +884,7 @@
     <row r="22" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -882,7 +894,7 @@
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -892,7 +904,7 @@
     <row r="24" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <f t="shared" si="1"/>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -902,7 +914,7 @@
     <row r="25" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="7">
         <f>SUM(B3:B24)</f>
-        <v>5016000</v>
+        <v>7235000</v>
       </c>
       <c r="C25" s="7">
         <f>SUM(C3:C24)</f>
@@ -916,7 +928,7 @@
       </c>
       <c r="C27" s="10">
         <f>A24</f>
-        <v>-2219000</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>8</v>
